--- a/BWI/bestwine_output/bestwine_Guatemala.xlsx
+++ b/BWI/bestwine_output/bestwine_Guatemala.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA54"/>
+  <dimension ref="A1:AA56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6445,6 +6445,224 @@
       <c r="Z54" s="2" t="inlineStr"/>
       <c r="AA54" s="2" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>7456</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Ciudad de Guatemala</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1273 6A Avenida</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>01010</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>servicioalcliente@vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>+502 2243 1515</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>29685508</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-uva-s.-a.</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotecagt/</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotecagt</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>Eddie Tabush</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eddie-tabush-714a2110</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>7456</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Ciudad de Guatemala</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1273 6A Avenida</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>01010</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>servicioalcliente@vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>+502 2243 1515</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>29685508</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-uva-s.-a.</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotecagt/</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotecagt</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Sotelo</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-sotelo-9a4337155/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Guatemala.xlsx
+++ b/BWI/bestwine_output/bestwine_Guatemala.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA56"/>
+  <dimension ref="A1:AA58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6663,6 +6663,224 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>7456</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Ciudad de Guatemala</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1273 6A Avenida</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>01010</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>servicioalcliente@vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>+502 2243 1515</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>29685508</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-uva-s.-a.</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotecagt/</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotecagt</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>Eddie Tabush</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eddie-tabush-714a2110</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>7456</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Ciudad de Guatemala</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1273 6A Avenida</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>01010</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>servicioalcliente@vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>+502 2243 1515</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>29685508</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-uva-s.-a.</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotecagt/</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotecagt</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Sotelo</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-sotelo-9a4337155/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Guatemala.xlsx
+++ b/BWI/bestwine_output/bestwine_Guatemala.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA58"/>
+  <dimension ref="A1:AA60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6881,6 +6881,224 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>7456</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Ciudad de Guatemala</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1273 6A Avenida</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>01010</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>servicioalcliente@vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>+502 2243 1515</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>29685508</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-uva-s.-a.</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotecagt/</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotecagt</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>Eddie Tabush</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eddie-tabush-714a2110</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>7456</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Ciudad de Guatemala</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1273 6A Avenida</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>01010</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>servicioalcliente@vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>+502 2243 1515</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>29685508</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-uva-s.-a.</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotecagt/</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotecagt</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Sotelo</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-sotelo-9a4337155/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Guatemala.xlsx
+++ b/BWI/bestwine_output/bestwine_Guatemala.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA60"/>
+  <dimension ref="A1:AA62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7099,6 +7099,224 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>7456</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Ciudad de Guatemala</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1273 6A Avenida</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>01010</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>servicioalcliente@vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>+502 2243 1515</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>29685508</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-uva-s.-a.</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotecagt/</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotecagt</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>Eddie Tabush</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eddie-tabush-714a2110</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteca S.a.</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>7456</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Ciudad de Guatemala</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1273 6A Avenida</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>01010</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>servicioalcliente@vinoteca.gt</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>+502 2243 1515</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>29685508</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-uva-s.-a.</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotecagt/</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinotecagt</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Sotelo</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-sotelo-9a4337155/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
